--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260612_212624.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
